--- a/artfynd/A 74117-2021 artfynd.xlsx
+++ b/artfynd/A 74117-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135653002</v>
       </c>
       <c r="B2" t="n">
-        <v>57781</v>
+        <v>57783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 74117-2021 artfynd.xlsx
+++ b/artfynd/A 74117-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135653002</v>
       </c>
       <c r="B2" t="n">
-        <v>57783</v>
+        <v>57784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 74117-2021 artfynd.xlsx
+++ b/artfynd/A 74117-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135653002</v>
       </c>
       <c r="B2" t="n">
-        <v>57784</v>
+        <v>57788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 74117-2021 artfynd.xlsx
+++ b/artfynd/A 74117-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135653002</v>
       </c>
       <c r="B2" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
